--- a/Sengo Financial Model.xlsx
+++ b/Sengo Financial Model.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="644">
   <si>
     <t xml:space="preserve">SENGO FINANCIAL DASHBOARD</t>
   </si>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">Grant Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Square Mini Grant + BGV Emerging Leaders Fellowship + W.E. Build in Tulsa Cohort (2025); declining as recurring revenue grows</t>
+    <t xml:space="preserve">BGV Emerging Leaders Fellowship + W.E. Build in Tulsa Cohort (2025); reduced $17.5K; declining as recurring revenue grows</t>
   </si>
   <si>
     <t xml:space="preserve">Services &amp; Consulting</t>
@@ -939,6 +939,9 @@
   </si>
   <si>
     <t xml:space="preserve">Grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: P&amp;L (BGV Fellowship, W.E. Build; reduced $17.5K)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: P&amp;L (Square, BGV Fellowship, W.E. Build)</t>
@@ -3210,7 +3213,7 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">Projections!B34</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">Projections!C34</f>
@@ -3232,7 +3235,7 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="n">
         <f aca="false">IF(B5&gt;0,(C5-B5)/B5,0)</f>
-        <v>0.486212243320561</v>
+        <v>0.619808815446808</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">IF(C5&gt;0,(D5-C5)/C5,0)</f>
@@ -3249,7 +3252,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">Projections!B36</f>
-        <v>192448.167</v>
+        <v>176575.667</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">Projections!C36</f>
@@ -3291,7 +3294,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">Projections!B39</f>
-        <v>96448.167</v>
+        <v>80575.667</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">Projections!C39</f>
@@ -3312,7 +3315,7 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">Projections!B40</f>
-        <v>0.454556095974663</v>
+        <v>0.413885623147611</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Projections!C40</f>
@@ -3354,7 +3357,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">Projections!B45</f>
-        <v>96448.167</v>
+        <v>80575.667</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">Projections!C45</f>
@@ -3375,19 +3378,19 @@
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">Projections!B48</f>
-        <v>101448.167</v>
+        <v>85575.667</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Projections!C48</f>
-        <v>347752.626956881</v>
+        <v>331880.126956881</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">Projections!D48</f>
-        <v>223913.486913762</v>
+        <v>208040.986913762</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">Projections!E48</f>
-        <v>701943.846870643</v>
+        <v>686071.346870643</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3480,7 +3483,7 @@
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">'Valuation &amp; Exit'!B12</f>
-        <v>1697448</v>
+        <v>1557448</v>
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">'Valuation &amp; Exit'!C12</f>
@@ -4496,7 +4499,7 @@
         <v>122</v>
       </c>
       <c r="B40" s="49" t="n">
-        <v>54656</v>
+        <v>37156</v>
       </c>
       <c r="C40" s="49" t="n">
         <v>40000</v>
@@ -5069,15 +5072,15 @@
       </c>
       <c r="C72" s="52" t="n">
         <f aca="false">Projections!B48</f>
-        <v>101448.167</v>
+        <v>85575.667</v>
       </c>
       <c r="D72" s="52" t="n">
         <f aca="false">Projections!C48</f>
-        <v>347752.626956881</v>
+        <v>331880.126956881</v>
       </c>
       <c r="E72" s="52" t="n">
         <f aca="false">Projections!D48</f>
-        <v>223913.486913762</v>
+        <v>208040.986913762</v>
       </c>
       <c r="F72" s="52" t="s">
         <v>177</v>
@@ -7414,14 +7417,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="50" t="n">
-        <v>54656</v>
-      </c>
-      <c r="D12" s="94" t="n">
-        <f aca="false">IF(B11&gt;0,(C11-B11)/B11,IF(C11&gt;0,1,0))</f>
-        <v>1</v>
+        <v>37156</v>
+      </c>
+      <c r="D12" s="94" t="s">
+        <v>303</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7434,17 +7436,17 @@
       </c>
       <c r="C13" s="48" t="n">
         <f aca="false">SUM(C6:C12)</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="D13" s="48" t="n">
         <f aca="false">IF(B13&gt;0,(C13-B13)/B13,0)</f>
-        <v>3.00198042211283</v>
+        <v>2.67191006997491</v>
       </c>
       <c r="E13" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -7453,7 +7455,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B16" s="50" t="n">
         <v>432</v>
@@ -7468,7 +7470,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -7485,7 +7487,7 @@
       </c>
       <c r="C19" s="48" t="n">
         <f aca="false">C13-C16</f>
-        <v>192497</v>
+        <v>174997</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
@@ -7500,7 +7502,7 @@
       </c>
       <c r="C20" s="94" t="n">
         <f aca="false">IF(C13&gt;0,C19/C13,0)</f>
-        <v>0.907230147845472</v>
+        <v>0.898891006312891</v>
       </c>
       <c r="D20" s="94"/>
       <c r="E20" s="94"/>
@@ -7522,7 +7524,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B23" s="93" t="n">
         <f aca="false">IF(B13&gt;0,B22/B13,0)</f>
@@ -7530,14 +7532,14 @@
       </c>
       <c r="C23" s="93" t="n">
         <f aca="false">IF(C13&gt;0,C22/C13,0)</f>
-        <v>0.472704907602471</v>
+        <v>0.51519665504081</v>
       </c>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">B19-B22</f>
@@ -7545,14 +7547,14 @@
       </c>
       <c r="C25" s="48" t="n">
         <f aca="false">C19-C22</f>
-        <v>92198</v>
+        <v>74698</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B26" s="50" t="n">
         <v>101</v>
@@ -7565,7 +7567,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -7582,17 +7584,17 @@
       </c>
       <c r="C29" s="48" t="n">
         <f aca="false">C25-C26</f>
-        <v>91965</v>
+        <v>74465</v>
       </c>
       <c r="D29" s="48" t="n">
         <f aca="false">IF(ABS(B29)&gt;0,(C29-B29)/ABS(B29),0)</f>
-        <v>63.0965563808238</v>
+        <v>51.2802160702228</v>
       </c>
       <c r="E29" s="48"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B30" s="94" t="n">
         <f aca="false">IF(B13&gt;0,B29/B13,0)</f>
@@ -7600,7 +7602,7 @@
       </c>
       <c r="C30" s="94" t="n">
         <f aca="false">IF(C13&gt;0,C29/C13,0)</f>
-        <v>0.433427121184272</v>
+        <v>0.382497521586596</v>
       </c>
       <c r="D30" s="94"/>
       <c r="E30" s="94"/>
@@ -7632,57 +7634,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="95" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C4" s="95" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D4" s="95" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F4" s="96" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H4" s="96" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I4" s="96" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J4" s="96" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K4" s="96" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L4" s="96" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M4" s="96" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7764,7 +7766,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="97" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B7" s="98" t="n">
         <v>4000</v>
@@ -7822,7 +7824,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="97" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B8" s="98" t="n">
         <v>3958</v>
@@ -8044,7 +8046,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B13" s="98" t="n">
         <f aca="false">-ABS(B11*0.1)</f>
@@ -8166,7 +8168,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -8592,7 +8594,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -8611,7 +8613,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="101" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B28" s="102" t="n">
         <f aca="false">B14-B25</f>
@@ -8733,7 +8735,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -8801,7 +8803,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B33" s="102" t="n">
         <f aca="false">B28+B32</f>
@@ -8862,7 +8864,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="101" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B34" s="102" t="n">
         <f aca="false">5000+B33</f>
@@ -8923,37 +8925,37 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="107" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="40" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="40" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="40" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="40" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -8972,7 +8974,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B44" s="23"/>
       <c r="C44" s="23"/>
@@ -8986,7 +8988,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
@@ -9000,7 +9002,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
@@ -9014,7 +9016,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
@@ -9028,7 +9030,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
@@ -9042,7 +9044,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
@@ -9056,7 +9058,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B50" s="108"/>
       <c r="C50" s="108"/>
@@ -9105,12 +9107,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9160,7 +9162,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">Assumptions!B9</f>
@@ -9181,7 +9183,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B8" s="109" t="n">
         <f aca="false">Assumptions!B11</f>
@@ -9202,7 +9204,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">Assumptions!B13</f>
@@ -9223,7 +9225,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B10" s="109" t="n">
         <f aca="false">Assumptions!B15</f>
@@ -9265,7 +9267,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">Assumptions!B19</f>
@@ -9286,7 +9288,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="42" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B14" s="109" t="n">
         <f aca="false">Assumptions!B21</f>
@@ -9307,7 +9309,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">Assumptions!B23</f>
@@ -9328,7 +9330,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">Assumptions!B25</f>
@@ -9605,7 +9607,7 @@
       </c>
       <c r="B32" s="109" t="n">
         <f aca="false">Assumptions!B40</f>
-        <v>54656</v>
+        <v>37156</v>
       </c>
       <c r="C32" s="109" t="n">
         <f aca="false">Assumptions!C40</f>
@@ -9647,7 +9649,7 @@
       </c>
       <c r="B34" s="48" t="n">
         <f aca="false">B6+B12+B17+B26+B32+B33</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="C34" s="48" t="n">
         <f aca="false">C6+C12+C17+C26+C32+C33</f>
@@ -9664,11 +9666,11 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B35" s="10" t="n">
         <f aca="false">-ABS(B34*Assumptions!B44)</f>
-        <v>-19732.833</v>
+        <v>-18105.333</v>
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">-ABS(C34*Assumptions!C44)</f>
@@ -9689,7 +9691,7 @@
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">B34+B35</f>
-        <v>192448.167</v>
+        <v>176575.667</v>
       </c>
       <c r="C36" s="48" t="n">
         <f aca="false">C34+C35</f>
@@ -9727,7 +9729,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" s="109" t="n">
         <f aca="false">-ABS(Assumptions!B68)</f>
@@ -9752,7 +9754,7 @@
       </c>
       <c r="B39" s="41" t="n">
         <f aca="false">B36+B38</f>
-        <v>96448.167</v>
+        <v>80575.667</v>
       </c>
       <c r="C39" s="41" t="n">
         <f aca="false">C36+C38</f>
@@ -9773,7 +9775,7 @@
       </c>
       <c r="B40" s="93" t="n">
         <f aca="false">IF(B34&gt;0,B39/B34,0)</f>
-        <v>0.454556095974663</v>
+        <v>0.413885623147611</v>
       </c>
       <c r="C40" s="93" t="n">
         <f aca="false">IF(C34&gt;0,C39/C34,0)</f>
@@ -9790,7 +9792,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -9799,7 +9801,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B42" s="109" t="n">
         <v>0</v>
@@ -9817,12 +9819,12 @@
         <v>-88475</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>0</v>
@@ -9840,12 +9842,12 @@
         <v>-23739.640043119</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" s="48" t="n">
         <f aca="false">B42+B43</f>
@@ -9870,7 +9872,7 @@
       </c>
       <c r="B45" s="41" t="n">
         <f aca="false">B39+B44</f>
-        <v>96448.167</v>
+        <v>80575.667</v>
       </c>
       <c r="C45" s="41" t="n">
         <f aca="false">C39+C44</f>
@@ -9887,11 +9889,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B46" s="93" t="n">
         <f aca="false">IF(B34&gt;0,B45/B34,0)</f>
-        <v>0.454556095974663</v>
+        <v>0.413885623147611</v>
       </c>
       <c r="C46" s="93" t="n">
         <f aca="false">IF(C34&gt;0,C45/C34,0)</f>
@@ -9929,28 +9931,28 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" s="48" t="n">
         <f aca="false">Assumptions!B72+B45+B47</f>
-        <v>101448.167</v>
+        <v>85575.667</v>
       </c>
       <c r="C48" s="48" t="n">
         <f aca="false">B48+C45+C47</f>
-        <v>347752.626956881</v>
+        <v>331880.126956881</v>
       </c>
       <c r="D48" s="48" t="n">
         <f aca="false">C48+D45+D47</f>
-        <v>223913.486913762</v>
+        <v>208040.986913762</v>
       </c>
       <c r="E48" s="48" t="n">
         <f aca="false">D48+E45+E47</f>
-        <v>701943.846870643</v>
+        <v>686071.346870643</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -9959,7 +9961,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" s="13" t="n">
         <f aca="false">Assumptions!B75</f>
@@ -9980,7 +9982,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B52" s="14" t="n">
         <f aca="false">Assumptions!B76</f>
@@ -10022,11 +10024,11 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B55" s="110" t="n">
         <f aca="false">B34/1</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="C55" s="110" t="n">
         <f aca="false">C34/4</f>
@@ -10089,17 +10091,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10117,12 +10119,12 @@
         <v>5</v>
       </c>
       <c r="F5" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -10147,12 +10149,12 @@
         <v>115000</v>
       </c>
       <c r="F7" s="50" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B8" s="49" t="n">
         <v>2000</v>
@@ -10167,12 +10169,12 @@
         <v>144000</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B9" s="50" t="n">
         <v>73890</v>
@@ -10187,7 +10189,7 @@
         <v>140000</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10207,7 +10209,7 @@
         <v>100000</v>
       </c>
       <c r="F10" s="49" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10227,7 +10229,7 @@
         <v>10000</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10247,7 +10249,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="49" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10274,7 +10276,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -10284,7 +10286,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B16" s="52" t="n">
         <f aca="false">-ABS(B13*0.093)</f>
@@ -10328,7 +10330,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B19" s="50" t="n">
         <v>7911</v>
@@ -10343,12 +10345,12 @@
         <v>72000</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B20" s="49" t="n">
         <v>2469</v>
@@ -10363,12 +10365,12 @@
         <v>36000</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B21" s="50" t="n">
         <v>25000</v>
@@ -10383,12 +10385,12 @@
         <v>80000</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B22" s="49" t="n">
         <v>15994</v>
@@ -10403,12 +10405,12 @@
         <v>25000</v>
       </c>
       <c r="F22" s="49" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B23" s="50" t="n">
         <v>8197</v>
@@ -10423,12 +10425,12 @@
         <v>20000</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B24" s="49" t="n">
         <v>5087</v>
@@ -10443,12 +10445,12 @@
         <v>25000</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B25" s="50" t="n">
         <v>3825</v>
@@ -10463,12 +10465,12 @@
         <v>12000</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B26" s="49" t="n">
         <v>12116</v>
@@ -10483,12 +10485,12 @@
         <v>18000</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B27" s="50" t="n">
         <v>5341</v>
@@ -10503,12 +10505,12 @@
         <v>12000</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B28" s="49" t="n">
         <v>5244</v>
@@ -10523,12 +10525,12 @@
         <v>10000</v>
       </c>
       <c r="F28" s="49" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B29" s="50" t="n">
         <v>9116</v>
@@ -10543,7 +10545,7 @@
         <v>15000</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10570,7 +10572,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -10624,7 +10626,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">5000+B33</f>
@@ -10646,7 +10648,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -10656,11 +10658,11 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B39" s="10" t="n">
         <f aca="false">Projections!B34</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="C39" s="10" t="n">
         <f aca="false">Projections!C34</f>
@@ -10678,7 +10680,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B40" s="52" t="n">
         <f aca="false">B13</f>
@@ -10700,11 +10702,11 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B41" s="110" t="n">
         <f aca="false">B39-B40</f>
-        <v>0</v>
+        <v>-17500</v>
       </c>
       <c r="C41" s="110" t="n">
         <f aca="false">C39-C40</f>
@@ -10722,11 +10724,11 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B43" s="10" t="n">
         <f aca="false">Projections!B39</f>
-        <v>96448.167</v>
+        <v>80575.667</v>
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">Projections!C39</f>
@@ -10744,7 +10746,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B44" s="52" t="n">
         <f aca="false">B33</f>
@@ -10766,29 +10768,29 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B46" s="109" t="n">
         <f aca="false">Projections!B48</f>
-        <v>101448.167</v>
+        <v>85575.667</v>
       </c>
       <c r="C46" s="109" t="n">
         <f aca="false">Projections!C48</f>
-        <v>347752.626956881</v>
+        <v>331880.126956881</v>
       </c>
       <c r="D46" s="109" t="n">
         <f aca="false">Projections!D48</f>
-        <v>223913.486913762</v>
+        <v>208040.986913762</v>
       </c>
       <c r="E46" s="109" t="n">
         <f aca="false">Projections!E48</f>
-        <v>701943.846870643</v>
+        <v>686071.346870643</v>
       </c>
       <c r="F46" s="109"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B47" s="110" t="n">
         <f aca="false">B36</f>
@@ -10810,10 +10812,10 @@
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="107" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B49" s="112" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C49" s="112"/>
       <c r="D49" s="112"/>
@@ -10850,17 +10852,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10878,21 +10880,21 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -10909,7 +10911,7 @@
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">Projections!B34</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">Projections!C34</f>
@@ -10936,7 +10938,7 @@
         <v>5972062.5</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10945,7 +10947,7 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">Projections!B45</f>
-        <v>96448.167</v>
+        <v>80575.667</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">Projections!C45</f>
@@ -10972,17 +10974,17 @@
         <v>1613352.46485447</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B8" s="93"/>
       <c r="C8" s="93" t="n">
         <f aca="false">IF(B6&gt;0,(C6-B6)/B6,0)</f>
-        <v>0.486212243320561</v>
+        <v>0.619808815446808</v>
       </c>
       <c r="D8" s="93" t="n">
         <f aca="false">IF(C6&gt;0,(D6-C6)/C6,0)</f>
@@ -11008,7 +11010,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B9" s="113" t="n">
         <v>0.5</v>
@@ -11020,12 +11022,12 @@
       <c r="G9" s="114"/>
       <c r="H9" s="114"/>
       <c r="I9" s="114" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -11038,11 +11040,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B11" s="115" t="n">
         <f aca="false">B6*5</f>
-        <v>1060905</v>
+        <v>973405</v>
       </c>
       <c r="C11" s="115" t="n">
         <f aca="false">C6*5</f>
@@ -11069,16 +11071,16 @@
         <v>29860312.5</v>
       </c>
       <c r="I11" s="115" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B12" s="116" t="n">
         <f aca="false">B6*8</f>
-        <v>1697448</v>
+        <v>1557448</v>
       </c>
       <c r="C12" s="116" t="n">
         <f aca="false">C6*8</f>
@@ -11105,16 +11107,16 @@
         <v>47776500</v>
       </c>
       <c r="I12" s="116" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B13" s="115" t="n">
         <f aca="false">B6*12</f>
-        <v>2546172</v>
+        <v>2336172</v>
       </c>
       <c r="C13" s="115" t="n">
         <f aca="false">C6*12</f>
@@ -11141,16 +11143,16 @@
         <v>71664750</v>
       </c>
       <c r="I13" s="115" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B14" s="116" t="n">
         <f aca="false">B6*15</f>
-        <v>3182715</v>
+        <v>2920215</v>
       </c>
       <c r="C14" s="116" t="n">
         <f aca="false">C6*15</f>
@@ -11177,12 +11179,12 @@
         <v>89580937.5</v>
       </c>
       <c r="I14" s="116" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -11195,11 +11197,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B17" s="115" t="n">
         <f aca="false">IF(B7&gt;0,B7*10,0)</f>
-        <v>964481.67</v>
+        <v>805756.67</v>
       </c>
       <c r="C17" s="115" t="n">
         <f aca="false">IF(C7&gt;0,C7*10,0)</f>
@@ -11226,16 +11228,16 @@
         <v>16133524.6485447</v>
       </c>
       <c r="I17" s="115" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B18" s="116" t="n">
         <f aca="false">IF(B7&gt;0,B7*15,0)</f>
-        <v>1446722.505</v>
+        <v>1208635.005</v>
       </c>
       <c r="C18" s="116" t="n">
         <f aca="false">IF(C7&gt;0,C7*15,0)</f>
@@ -11262,16 +11264,16 @@
         <v>24200286.9728171</v>
       </c>
       <c r="I18" s="116" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B19" s="115" t="n">
         <f aca="false">IF(B7&gt;0,B7*25,0)</f>
-        <v>2411204.175</v>
+        <v>2014391.675</v>
       </c>
       <c r="C19" s="115" t="n">
         <f aca="false">IF(C7&gt;0,C7*25,0)</f>
@@ -11298,12 +11300,12 @@
         <v>40333811.6213618</v>
       </c>
       <c r="I19" s="115" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -11347,12 +11349,12 @@
         <v>250000</v>
       </c>
       <c r="I22" s="109" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="67" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B24" s="68"/>
       <c r="C24" s="68"/>
@@ -11362,12 +11364,12 @@
       <c r="G24" s="68"/>
       <c r="H24" s="68"/>
       <c r="I24" s="68" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="44" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B25" s="117" t="n">
         <f aca="false">IF(3000000&gt;0,B22/3000000,0)</f>
@@ -11398,16 +11400,16 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="I25" s="117" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="42" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" s="118" t="n">
         <f aca="false">B25*B12</f>
-        <v>141454</v>
+        <v>129787.333333333</v>
       </c>
       <c r="C26" s="118" t="n">
         <f aca="false">C25*C12</f>
@@ -11434,16 +11436,16 @@
         <v>3981375</v>
       </c>
       <c r="I26" s="118" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="44" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B27" s="45" t="n">
         <f aca="false">B25*B13</f>
-        <v>212181</v>
+        <v>194681</v>
       </c>
       <c r="C27" s="45" t="n">
         <f aca="false">C25*C13</f>
@@ -11470,16 +11472,16 @@
         <v>5972062.5</v>
       </c>
       <c r="I27" s="45" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="42" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B28" s="119" t="n">
         <f aca="false">IF(B22&gt;0,B26/B22,0)</f>
-        <v>0.565816</v>
+        <v>0.519149333333333</v>
       </c>
       <c r="C28" s="119" t="n">
         <f aca="false">IF(B22&gt;0,C26/B22,0)</f>
@@ -11506,12 +11508,12 @@
         <v>15.9255</v>
       </c>
       <c r="I28" s="119" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="67" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B29" s="68"/>
       <c r="C29" s="68"/>
@@ -11521,12 +11523,12 @@
       <c r="G29" s="68"/>
       <c r="H29" s="68"/>
       <c r="I29" s="68" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="42" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B30" s="120" t="n">
         <f aca="false">IF(Dashboard!B32&gt;0,B22/Dashboard!B32,0)</f>
@@ -11557,16 +11559,16 @@
         <v>0.05</v>
       </c>
       <c r="I30" s="120" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="44" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B31" s="45" t="n">
         <f aca="false">B30*B12</f>
-        <v>84872.4</v>
+        <v>77872.4</v>
       </c>
       <c r="C31" s="45" t="n">
         <f aca="false">C30*C12</f>
@@ -11593,16 +11595,16 @@
         <v>2388825</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="42" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B32" s="118" t="n">
         <f aca="false">B30*B13</f>
-        <v>127308.6</v>
+        <v>116808.6</v>
       </c>
       <c r="C32" s="118" t="n">
         <f aca="false">C30*C13</f>
@@ -11629,16 +11631,16 @@
         <v>3583237.5</v>
       </c>
       <c r="I32" s="118" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B33" s="121" t="n">
         <f aca="false">IF(B22&gt;0,B31/B22,0)</f>
-        <v>0.3394896</v>
+        <v>0.3114896</v>
       </c>
       <c r="C33" s="121" t="n">
         <f aca="false">IF(B22&gt;0,C31/B22,0)</f>
@@ -11665,12 +11667,12 @@
         <v>9.5553</v>
       </c>
       <c r="I33" s="121" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B34" s="68"/>
       <c r="C34" s="68"/>
@@ -11680,12 +11682,12 @@
       <c r="G34" s="68"/>
       <c r="H34" s="68"/>
       <c r="I34" s="68" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B35" s="117" t="n">
         <f aca="false">IF(8000000&gt;0,B22/8000000,0)</f>
@@ -11716,16 +11718,16 @@
         <v>0.03125</v>
       </c>
       <c r="I35" s="117" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="42" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B36" s="118" t="n">
         <f aca="false">B35*B12</f>
-        <v>53045.25</v>
+        <v>48670.25</v>
       </c>
       <c r="C36" s="118" t="n">
         <f aca="false">C35*C12</f>
@@ -11752,16 +11754,16 @@
         <v>1493015.625</v>
       </c>
       <c r="I36" s="118" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B37" s="45" t="n">
         <f aca="false">B35*B13</f>
-        <v>79567.875</v>
+        <v>73005.375</v>
       </c>
       <c r="C37" s="45" t="n">
         <f aca="false">C35*C13</f>
@@ -11788,16 +11790,16 @@
         <v>2239523.4375</v>
       </c>
       <c r="I37" s="45" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="42" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B38" s="119" t="n">
         <f aca="false">IF(B22&gt;0,B36/B22,0)</f>
-        <v>0.212181</v>
+        <v>0.194681</v>
       </c>
       <c r="C38" s="119" t="n">
         <f aca="false">IF(B22&gt;0,C36/B22,0)</f>
@@ -11824,12 +11826,12 @@
         <v>5.9720625</v>
       </c>
       <c r="I38" s="119" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -11855,12 +11857,12 @@
       <c r="G40" s="109"/>
       <c r="H40" s="109"/>
       <c r="I40" s="109" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B41" s="122" t="n">
         <f aca="false">Dashboard!B28</f>
@@ -11873,12 +11875,12 @@
       <c r="G41" s="122"/>
       <c r="H41" s="122"/>
       <c r="I41" s="122" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B42" s="15" t="n">
         <f aca="false">Dashboard!B29</f>
@@ -11891,12 +11893,12 @@
       <c r="G42" s="15"/>
       <c r="H42" s="15"/>
       <c r="I42" s="15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B43" s="41" t="n">
         <f aca="false">B40*B42</f>
@@ -11909,16 +11911,16 @@
       <c r="G43" s="41"/>
       <c r="H43" s="41"/>
       <c r="I43" s="41" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B45" s="10" t="n">
         <f aca="false">B6*B41</f>
-        <v>10609.05</v>
+        <v>9734.05</v>
       </c>
       <c r="C45" s="10" t="n">
         <f aca="false">C6*B41</f>
@@ -11945,28 +11947,28 @@
         <v>298603.125</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B46" s="48" t="n">
         <f aca="false">MIN(B45,B43)</f>
-        <v>10609.05</v>
+        <v>9734.05</v>
       </c>
       <c r="C46" s="48" t="n">
         <f aca="false">MIN(B46+C45,B43)</f>
-        <v>26376.35</v>
+        <v>25501.35</v>
       </c>
       <c r="D46" s="48" t="n">
         <f aca="false">MIN(C46+D45,B43)</f>
-        <v>66252.85</v>
+        <v>65377.85</v>
       </c>
       <c r="E46" s="48" t="n">
         <f aca="false">MIN(D46+E45,B43)</f>
-        <v>154727.85</v>
+        <v>153852.85</v>
       </c>
       <c r="F46" s="48" t="n">
         <f aca="false">MIN(E46+F45,B43)</f>
@@ -11981,28 +11983,28 @@
         <v>225000</v>
       </c>
       <c r="I46" s="48" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B47" s="110" t="n">
         <f aca="false">MAX(0,B43-B46)</f>
-        <v>214390.95</v>
+        <v>215265.95</v>
       </c>
       <c r="C47" s="110" t="n">
         <f aca="false">MAX(0,B43-C46)</f>
-        <v>198623.65</v>
+        <v>199498.65</v>
       </c>
       <c r="D47" s="110" t="n">
         <f aca="false">MAX(0,B43-D46)</f>
-        <v>158747.15</v>
+        <v>159622.15</v>
       </c>
       <c r="E47" s="110" t="n">
         <f aca="false">MAX(0,B43-E46)</f>
-        <v>70272.15</v>
+        <v>71147.15</v>
       </c>
       <c r="F47" s="110" t="n">
         <f aca="false">MAX(0,B43-F46)</f>
@@ -12017,12 +12019,12 @@
         <v>0</v>
       </c>
       <c r="I47" s="110" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B48" s="123" t="str">
         <f aca="false">IF(B47&lt;=0,"YES","NO")</f>
@@ -12056,7 +12058,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -12082,12 +12084,12 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B52" s="8" t="n">
         <f aca="false">Dashboard!B30</f>
@@ -12100,12 +12102,12 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B53" s="13" t="n">
         <f aca="false">Dashboard!B31</f>
@@ -12118,12 +12120,12 @@
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
       <c r="I53" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">PMT(B52,B53,-B51)</f>
@@ -12136,12 +12138,12 @@
       <c r="G54" s="48"/>
       <c r="H54" s="48"/>
       <c r="I54" s="48" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B56" s="52" t="n">
         <v>0</v>
@@ -12170,12 +12172,12 @@
         <v>0</v>
       </c>
       <c r="I56" s="52" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B57" s="110" t="n">
         <f aca="false">B56</f>
@@ -12209,7 +12211,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B58" s="52" t="n">
         <f aca="false">B54*B53-B51</f>
@@ -12222,12 +12224,12 @@
       <c r="G58" s="52"/>
       <c r="H58" s="52"/>
       <c r="I58" s="52" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -12240,7 +12242,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B61" s="6" t="n">
         <f aca="false">Dashboard!B26</f>
@@ -12253,12 +12255,12 @@
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="42" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B62" s="118" t="n">
         <f aca="false">B22</f>
@@ -12277,7 +12279,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="44" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B63" s="45" t="n">
         <f aca="false">B40</f>
@@ -12296,7 +12298,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B64" s="118" t="n">
         <f aca="false">B51</f>
@@ -12315,11 +12317,11 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B66" s="48" t="n">
         <f aca="false">B45+B56</f>
-        <v>10609.05</v>
+        <v>9734.05</v>
       </c>
       <c r="C66" s="48" t="n">
         <f aca="false">C45+C56</f>
@@ -12346,12 +12348,12 @@
         <v>298603.125</v>
       </c>
       <c r="I66" s="48" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B67" s="94" t="n">
         <f aca="false">IF(B6&gt;0,B66/B6,0)</f>
@@ -12385,7 +12387,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B69" s="122" t="n">
         <f aca="false">Dashboard!B34</f>
@@ -12398,7 +12400,7 @@
       <c r="G69" s="122"/>
       <c r="H69" s="122"/>
       <c r="I69" s="122" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12419,7 +12421,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="17" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -12432,7 +12434,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B73" s="23"/>
       <c r="C73" s="23"/>
@@ -12445,7 +12447,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="17" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -12458,182 +12460,182 @@
     </row>
     <row r="76" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>287</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="125" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B77" s="125" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C77" s="125" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D77" s="126" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E77" s="126" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F77" s="125" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G77" s="125"/>
       <c r="H77" s="125"/>
       <c r="I77" s="126" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="127" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B78" s="127" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C78" s="127" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D78" s="128" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E78" s="128" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F78" s="127" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G78" s="127"/>
       <c r="H78" s="127"/>
       <c r="I78" s="128" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="125" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B79" s="125" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C79" s="125" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D79" s="126" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E79" s="126" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F79" s="125" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G79" s="125"/>
       <c r="H79" s="125"/>
       <c r="I79" s="126" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="127" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B80" s="127" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C80" s="127" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D80" s="128" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E80" s="128" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F80" s="127" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G80" s="127"/>
       <c r="H80" s="127"/>
       <c r="I80" s="128" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="125" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B81" s="125" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C81" s="125" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D81" s="126" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E81" s="126" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F81" s="125" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G81" s="125"/>
       <c r="H81" s="125"/>
       <c r="I81" s="126" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="127" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B82" s="127" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C82" s="127" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D82" s="128" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E82" s="128" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F82" s="127" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G82" s="127"/>
       <c r="H82" s="127"/>
       <c r="I82" s="128" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="17" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -12646,182 +12648,182 @@
     </row>
     <row r="86" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="125" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B87" s="125" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C87" s="125" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D87" s="125" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E87" s="125" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F87" s="125" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G87" s="125"/>
       <c r="H87" s="125"/>
       <c r="I87" s="126" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="127" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B88" s="127" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C88" s="127" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D88" s="127" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E88" s="127" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F88" s="127" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G88" s="127"/>
       <c r="H88" s="127"/>
       <c r="I88" s="128" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="125" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B89" s="125" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C89" s="125" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D89" s="125" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E89" s="125" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F89" s="125" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G89" s="125"/>
       <c r="H89" s="125"/>
       <c r="I89" s="126" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="127" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B90" s="127" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C90" s="127" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D90" s="127" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E90" s="127" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F90" s="127" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G90" s="127"/>
       <c r="H90" s="127"/>
       <c r="I90" s="128" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="125" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B91" s="125" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C91" s="125" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D91" s="125" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E91" s="125" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F91" s="125" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G91" s="125"/>
       <c r="H91" s="125"/>
       <c r="I91" s="126" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="127" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B92" s="127" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C92" s="127" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D92" s="127" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E92" s="127" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F92" s="127" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G92" s="127"/>
       <c r="H92" s="127"/>
       <c r="I92" s="128" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="17" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
@@ -12834,7 +12836,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="23" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B96" s="23"/>
       <c r="C96" s="23"/>
@@ -12847,232 +12849,232 @@
     </row>
     <row r="97" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="125" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B98" s="125" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C98" s="126" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D98" s="126" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E98" s="126" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F98" s="125" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G98" s="125"/>
       <c r="H98" s="125"/>
       <c r="I98" s="126" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="127" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B99" s="127" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C99" s="128" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D99" s="128" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E99" s="128" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F99" s="127" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G99" s="127"/>
       <c r="H99" s="127"/>
       <c r="I99" s="128" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="125" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B100" s="125" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C100" s="126" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D100" s="126" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E100" s="126" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F100" s="125" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G100" s="125"/>
       <c r="H100" s="125"/>
       <c r="I100" s="126" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="127" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B101" s="127" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C101" s="128" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D101" s="128" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E101" s="128" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F101" s="127" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G101" s="127"/>
       <c r="H101" s="127"/>
       <c r="I101" s="128" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="125" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B102" s="125" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C102" s="126" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D102" s="126" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E102" s="126" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F102" s="125" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G102" s="125"/>
       <c r="H102" s="125"/>
       <c r="I102" s="126" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="127" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B103" s="127" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C103" s="128" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D103" s="128" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E103" s="128" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F103" s="127" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G103" s="127"/>
       <c r="H103" s="127"/>
       <c r="I103" s="128" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="125" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B104" s="125" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C104" s="126" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D104" s="126" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E104" s="126" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F104" s="125" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G104" s="125"/>
       <c r="H104" s="125"/>
       <c r="I104" s="126" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="127" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B105" s="127" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C105" s="128" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D105" s="128" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E105" s="128" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F105" s="127" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G105" s="127"/>
       <c r="H105" s="127"/>
       <c r="I105" s="128" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13085,7 +13087,7 @@
     </row>
     <row r="109" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="129" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B109" s="129"/>
       <c r="C109" s="129"/>
@@ -13098,7 +13100,7 @@
     </row>
     <row r="111" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="130" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B111" s="130"/>
       <c r="C111" s="130"/>

--- a/Sengo Financial Model.xlsx
+++ b/Sengo Financial Model.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="647">
   <si>
     <t xml:space="preserve">SENGO FINANCIAL DASHBOARD</t>
   </si>
@@ -917,6 +917,9 @@
     <t xml:space="preserve">Events Income</t>
   </si>
   <si>
+    <t xml:space="preserve">Source: Updated QB P&amp;L (Mar 20, 2026)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source: P&amp;L ($3,250 reclassified to B2B/Sponsorships)</t>
   </si>
   <si>
@@ -935,6 +938,9 @@
     <t xml:space="preserve">B2B / Sponsorships</t>
   </si>
   <si>
+    <t xml:space="preserve">Source: P&amp;L (partner deployments + sponsorships)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source: P&amp;L (partner deployments + sponsorships reclassified)</t>
   </si>
   <si>
@@ -953,6 +959,9 @@
     <t xml:space="preserve">COGS</t>
   </si>
   <si>
+    <t xml:space="preserve">Source: Updated QB P&amp;L (includes Events-COGS $20,944 + Processing $2,767)</t>
+  </si>
+  <si>
     <t xml:space="preserve">PROFITABILITY</t>
   </si>
   <si>
@@ -1049,7 +1058,7 @@
     <t xml:space="preserve">Jan/Feb Total Revenue &amp; Total OpEx match QuickBooks P&amp;L exactly.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mar coaching includes $10K deferred payout. Apr B2B includes $5,540 confirmed partnership.</t>
+    <t xml:space="preserve">Mar coaching includes $10K deferred payout. Apr B2B $5,540 partnership is now Accounts Receivable (not recognized until collected).</t>
   </si>
   <si>
     <t xml:space="preserve">FxF NYC vendor payments collected Dec/Jan; shown in Events when received per QB.</t>
@@ -3213,7 +3222,7 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">Projections!B34</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">Projections!C34</f>
@@ -3235,7 +3244,7 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="n">
         <f aca="false">IF(B5&gt;0,(C5-B5)/B5,0)</f>
-        <v>0.619808815446808</v>
+        <v>0.76988657091703</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">IF(C5&gt;0,(D5-C5)/C5,0)</f>
@@ -3252,7 +3261,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">Projections!B36</f>
-        <v>176575.667</v>
+        <v>161602.911</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">Projections!C36</f>
@@ -3294,7 +3303,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">Projections!B39</f>
-        <v>80575.667</v>
+        <v>65602.911</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">Projections!C39</f>
@@ -3315,7 +3324,7 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">Projections!B40</f>
-        <v>0.413885623147611</v>
+        <v>0.368197824586217</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Projections!C40</f>
@@ -3357,7 +3366,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">Projections!B45</f>
-        <v>80575.667</v>
+        <v>65602.911</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">Projections!C45</f>
@@ -3378,19 +3387,19 @@
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">Projections!B48</f>
-        <v>85575.667</v>
+        <v>70602.911</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Projections!C48</f>
-        <v>331880.126956881</v>
+        <v>316907.370956881</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">Projections!D48</f>
-        <v>208040.986913762</v>
+        <v>193068.230913762</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">Projections!E48</f>
-        <v>686071.346870643</v>
+        <v>671098.590870643</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3483,7 +3492,7 @@
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">'Valuation &amp; Exit'!B12</f>
-        <v>1557448</v>
+        <v>1425384</v>
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">'Valuation &amp; Exit'!C12</f>
@@ -4218,7 +4227,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>70640</v>
+        <v>57382</v>
       </c>
       <c r="C25" s="41" t="n">
         <f aca="false">SUM(C26:C32)</f>
@@ -4376,7 +4385,7 @@
       </c>
       <c r="B34" s="48" t="n">
         <f aca="false">SUM(B35:B39)</f>
-        <v>18250</v>
+        <v>15000</v>
       </c>
       <c r="C34" s="48" t="n">
         <f aca="false">SUM(C35:C39)</f>
@@ -4479,7 +4488,7 @@
         <v>120</v>
       </c>
       <c r="B39" s="47" t="n">
-        <v>18250</v>
+        <v>15000</v>
       </c>
       <c r="C39" s="47" t="n">
         <v>0</v>
@@ -5072,15 +5081,15 @@
       </c>
       <c r="C72" s="52" t="n">
         <f aca="false">Projections!B48</f>
-        <v>85575.667</v>
+        <v>70602.911</v>
       </c>
       <c r="D72" s="52" t="n">
         <f aca="false">Projections!C48</f>
-        <v>331880.126956881</v>
+        <v>316907.370956881</v>
       </c>
       <c r="E72" s="52" t="n">
         <f aca="false">Projections!D48</f>
-        <v>208040.986913762</v>
+        <v>193068.230913762</v>
       </c>
       <c r="F72" s="52" t="s">
         <v>177</v>
@@ -5608,39 +5617,39 @@
       </c>
       <c r="E9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!E11</f>
-        <v>12548.1907400079</v>
+        <v>7067.38345864662</v>
       </c>
       <c r="F9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!F11</f>
-        <v>19449.683419074</v>
+        <v>19693.2748538012</v>
       </c>
       <c r="G9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!G11</f>
-        <v>56871.2655583435</v>
+        <v>57480.2441451614</v>
       </c>
       <c r="H9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!H11</f>
-        <v>25523.3975917237</v>
+        <v>26132.3761785416</v>
       </c>
       <c r="I9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!I11</f>
-        <v>17052.0270224433</v>
+        <v>17661.0056092613</v>
       </c>
       <c r="J9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!J11</f>
-        <v>52986.8513330753</v>
+        <v>53961.217071984</v>
       </c>
       <c r="K9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!K11</f>
-        <v>20378.3986658375</v>
+        <v>20987.3772526554</v>
       </c>
       <c r="L9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!L11</f>
-        <v>50091.8973547228</v>
+        <v>51066.2630936315</v>
       </c>
       <c r="M9" s="71" t="n">
         <f aca="false">'2026 Monthly P&amp;L'!M11</f>
-        <v>25414.2883147719</v>
+        <v>26266.858336317</v>
       </c>
       <c r="N9" s="72" t="n">
         <f aca="false">SUM(B9:M9)</f>
@@ -5668,39 +5677,39 @@
       </c>
       <c r="E10" s="73" t="n">
         <f aca="false">E6+E7+E8+E9</f>
-        <v>12548.1907400079</v>
+        <v>7067.38345864662</v>
       </c>
       <c r="F10" s="73" t="n">
         <f aca="false">F6+F7+F8+F9</f>
-        <v>19449.683419074</v>
+        <v>19693.2748538012</v>
       </c>
       <c r="G10" s="73" t="n">
         <f aca="false">G6+G7+G8+G9</f>
-        <v>56871.2655583435</v>
+        <v>57480.2441451614</v>
       </c>
       <c r="H10" s="73" t="n">
         <f aca="false">H6+H7+H8+H9</f>
-        <v>25523.3975917237</v>
+        <v>26132.3761785416</v>
       </c>
       <c r="I10" s="73" t="n">
         <f aca="false">I6+I7+I8+I9</f>
-        <v>17052.0270224433</v>
+        <v>17661.0056092613</v>
       </c>
       <c r="J10" s="73" t="n">
         <f aca="false">J6+J7+J8+J9</f>
-        <v>52986.8513330753</v>
+        <v>53961.217071984</v>
       </c>
       <c r="K10" s="73" t="n">
         <f aca="false">K6+K7+K8+K9</f>
-        <v>20378.3986658375</v>
+        <v>20987.3772526554</v>
       </c>
       <c r="L10" s="73" t="n">
         <f aca="false">L6+L7+L8+L9</f>
-        <v>50091.8973547228</v>
+        <v>51066.2630936315</v>
       </c>
       <c r="M10" s="73" t="n">
         <f aca="false">M6+M7+M8+M9</f>
-        <v>25414.2883147719</v>
+        <v>26266.858336317</v>
       </c>
       <c r="N10" s="73" t="n">
         <f aca="false">SUM(B10:M10)</f>
@@ -5725,35 +5734,35 @@
       </c>
       <c r="E11" s="75" t="n">
         <f aca="false">D11+E10</f>
-        <v>47578.1907400079</v>
+        <v>42097.3834586466</v>
       </c>
       <c r="F11" s="75" t="n">
         <f aca="false">E11+F10</f>
-        <v>67027.8741590819</v>
+        <v>61790.6583124478</v>
       </c>
       <c r="G11" s="75" t="n">
         <f aca="false">F11+G10</f>
-        <v>123899.139717425</v>
+        <v>119270.902457609</v>
       </c>
       <c r="H11" s="75" t="n">
         <f aca="false">G11+H10</f>
-        <v>149422.537309149</v>
+        <v>145403.278636151</v>
       </c>
       <c r="I11" s="75" t="n">
         <f aca="false">H11+I10</f>
-        <v>166474.564331592</v>
+        <v>163064.284245412</v>
       </c>
       <c r="J11" s="75" t="n">
         <f aca="false">I11+J10</f>
-        <v>219461.415664668</v>
+        <v>217025.501317396</v>
       </c>
       <c r="K11" s="75" t="n">
         <f aca="false">J11+K10</f>
-        <v>239839.814330505</v>
+        <v>238012.878570052</v>
       </c>
       <c r="L11" s="75" t="n">
         <f aca="false">K11+L10</f>
-        <v>289931.711685228</v>
+        <v>289079.141663683</v>
       </c>
       <c r="M11" s="75" t="n">
         <f aca="false">L11+M10</f>
@@ -6697,35 +6706,35 @@
       </c>
       <c r="F34" s="84" t="n">
         <f aca="false">E37</f>
-        <v>52578.1907400079</v>
+        <v>47097.3834586466</v>
       </c>
       <c r="G34" s="84" t="n">
         <f aca="false">F37</f>
-        <v>72027.8741590819</v>
+        <v>66790.6583124478</v>
       </c>
       <c r="H34" s="84" t="n">
         <f aca="false">G37</f>
-        <v>128899.139717425</v>
+        <v>124270.902457609</v>
       </c>
       <c r="I34" s="84" t="n">
         <f aca="false">H37</f>
-        <v>154422.537309149</v>
+        <v>150403.278636151</v>
       </c>
       <c r="J34" s="84" t="n">
         <f aca="false">I37</f>
-        <v>171474.564331592</v>
+        <v>168064.284245412</v>
       </c>
       <c r="K34" s="84" t="n">
         <f aca="false">J37</f>
-        <v>224461.415664668</v>
+        <v>222025.501317396</v>
       </c>
       <c r="L34" s="84" t="n">
         <f aca="false">K37</f>
-        <v>244839.814330505</v>
+        <v>243012.878570052</v>
       </c>
       <c r="M34" s="84" t="n">
         <f aca="false">L37</f>
-        <v>294931.711685228</v>
+        <v>294079.141663683</v>
       </c>
       <c r="O34" s="60" t="s">
         <v>249</v>
@@ -6749,39 +6758,39 @@
       </c>
       <c r="E35" s="76" t="n">
         <f aca="false">E10</f>
-        <v>12548.1907400079</v>
+        <v>7067.38345864662</v>
       </c>
       <c r="F35" s="76" t="n">
         <f aca="false">F10</f>
-        <v>19449.683419074</v>
+        <v>19693.2748538012</v>
       </c>
       <c r="G35" s="76" t="n">
         <f aca="false">G10</f>
-        <v>56871.2655583435</v>
+        <v>57480.2441451614</v>
       </c>
       <c r="H35" s="76" t="n">
         <f aca="false">H10</f>
-        <v>25523.3975917237</v>
+        <v>26132.3761785416</v>
       </c>
       <c r="I35" s="76" t="n">
         <f aca="false">I10</f>
-        <v>17052.0270224433</v>
+        <v>17661.0056092613</v>
       </c>
       <c r="J35" s="76" t="n">
         <f aca="false">J10</f>
-        <v>52986.8513330753</v>
+        <v>53961.217071984</v>
       </c>
       <c r="K35" s="76" t="n">
         <f aca="false">K10</f>
-        <v>20378.3986658375</v>
+        <v>20987.3772526554</v>
       </c>
       <c r="L35" s="76" t="n">
         <f aca="false">L10</f>
-        <v>50091.8973547228</v>
+        <v>51066.2630936315</v>
       </c>
       <c r="M35" s="76" t="n">
         <f aca="false">M10</f>
-        <v>25414.2883147719</v>
+        <v>26266.858336317</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6855,35 +6864,35 @@
       </c>
       <c r="E37" s="73" t="n">
         <f aca="false">E34+E35+E36</f>
-        <v>52578.1907400079</v>
+        <v>47097.3834586466</v>
       </c>
       <c r="F37" s="73" t="n">
         <f aca="false">F34+F35+F36</f>
-        <v>72027.8741590819</v>
+        <v>66790.6583124478</v>
       </c>
       <c r="G37" s="73" t="n">
         <f aca="false">G34+G35+G36</f>
-        <v>128899.139717425</v>
+        <v>124270.902457609</v>
       </c>
       <c r="H37" s="73" t="n">
         <f aca="false">H34+H35+H36</f>
-        <v>154422.537309149</v>
+        <v>150403.278636151</v>
       </c>
       <c r="I37" s="73" t="n">
         <f aca="false">I34+I35+I36</f>
-        <v>171474.564331592</v>
+        <v>168064.284245412</v>
       </c>
       <c r="J37" s="73" t="n">
         <f aca="false">J34+J35+J36</f>
-        <v>224461.415664668</v>
+        <v>222025.501317396</v>
       </c>
       <c r="K37" s="73" t="n">
         <f aca="false">K34+K35+K36</f>
-        <v>244839.814330505</v>
+        <v>243012.878570052</v>
       </c>
       <c r="L37" s="73" t="n">
         <f aca="false">L34+L35+L36</f>
-        <v>294931.711685228</v>
+        <v>294079.141663683</v>
       </c>
       <c r="M37" s="73" t="n">
         <f aca="false">M34+M35+M36</f>
@@ -7309,32 +7318,30 @@
         <v>29832</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>44344</v>
-      </c>
-      <c r="D6" s="93" t="n">
-        <f aca="false">IF(B6&gt;0,(C6-B6)/B6,IF(C6&gt;0,1,0))</f>
-        <v>0.486457495307053</v>
+        <v>46720</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>295</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B7" s="50" t="n">
         <v>2520</v>
       </c>
       <c r="C7" s="50" t="n">
-        <v>26296</v>
-      </c>
-      <c r="D7" s="94" t="n">
-        <f aca="false">IF(B7&gt;0,(C7-B7)/B7,IF(C7&gt;0,1,0))</f>
-        <v>9.43492063492064</v>
+        <v>10662</v>
+      </c>
+      <c r="D7" s="94" t="s">
+        <v>295</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7352,12 +7359,12 @@
         <v>1.34213964290899</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B9" s="50" t="n">
         <v>0</v>
@@ -7370,12 +7377,12 @@
         <v>1</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B10" s="49" t="n">
         <v>0</v>
@@ -7388,30 +7395,29 @@
         <v>1</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B11" s="50" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="50" t="n">
-        <v>18250</v>
-      </c>
-      <c r="D11" s="94" t="n">
-        <f aca="false">IF(B11&gt;0,(C11-B11)/B11,IF(C11&gt;0,1,0))</f>
-        <v>1</v>
+        <v>15000</v>
+      </c>
+      <c r="D11" s="94" t="s">
+        <v>302</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B12" s="50" t="n">
         <v>0</v>
@@ -7420,10 +7426,10 @@
         <v>37156</v>
       </c>
       <c r="D12" s="94" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7436,17 +7442,17 @@
       </c>
       <c r="C13" s="48" t="n">
         <f aca="false">SUM(C6:C12)</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="D13" s="48" t="n">
         <f aca="false">IF(B13&gt;0,(C13-B13)/B13,0)</f>
-        <v>2.67191006997491</v>
+        <v>2.36054999151248</v>
       </c>
       <c r="E13" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -7455,22 +7461,24 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B16" s="50" t="n">
         <v>432</v>
       </c>
       <c r="C16" s="50" t="n">
-        <v>19684</v>
-      </c>
-      <c r="D16" s="50"/>
+        <v>23711</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>309</v>
+      </c>
       <c r="E16" s="50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -7487,7 +7495,7 @@
       </c>
       <c r="C19" s="48" t="n">
         <f aca="false">C13-C16</f>
-        <v>174997</v>
+        <v>154462</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
@@ -7502,7 +7510,7 @@
       </c>
       <c r="C20" s="94" t="n">
         <f aca="false">IF(C13&gt;0,C19/C13,0)</f>
-        <v>0.898891006312891</v>
+        <v>0.866921475195456</v>
       </c>
       <c r="D20" s="94"/>
       <c r="E20" s="94"/>
@@ -7515,16 +7523,18 @@
         <v>53967</v>
       </c>
       <c r="C22" s="50" t="n">
-        <v>100299</v>
-      </c>
-      <c r="D22" s="50"/>
+        <v>96272</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>295</v>
+      </c>
       <c r="E22" s="50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B23" s="93" t="n">
         <f aca="false">IF(B13&gt;0,B22/B13,0)</f>
@@ -7532,14 +7542,14 @@
       </c>
       <c r="C23" s="93" t="n">
         <f aca="false">IF(C13&gt;0,C22/C13,0)</f>
-        <v>0.51519665504081</v>
+        <v>0.540328781577456</v>
       </c>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">B19-B22</f>
@@ -7547,14 +7557,14 @@
       </c>
       <c r="C25" s="48" t="n">
         <f aca="false">C19-C22</f>
-        <v>74698</v>
+        <v>58190</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B26" s="50" t="n">
         <v>101</v>
@@ -7567,7 +7577,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -7584,17 +7594,17 @@
       </c>
       <c r="C29" s="48" t="n">
         <f aca="false">C25-C26</f>
-        <v>74465</v>
+        <v>57957</v>
       </c>
       <c r="D29" s="48" t="n">
         <f aca="false">IF(ABS(B29)&gt;0,(C29-B29)/ABS(B29),0)</f>
-        <v>51.2802160702228</v>
+        <v>40.1336934503714</v>
       </c>
       <c r="E29" s="48"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B30" s="94" t="n">
         <f aca="false">IF(B13&gt;0,B29/B13,0)</f>
@@ -7602,7 +7612,7 @@
       </c>
       <c r="C30" s="94" t="n">
         <f aca="false">IF(C13&gt;0,C29/C13,0)</f>
-        <v>0.382497521586596</v>
+        <v>0.32528497583809</v>
       </c>
       <c r="D30" s="94"/>
       <c r="E30" s="94"/>
@@ -7634,57 +7644,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="95" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C4" s="95" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D4" s="95" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F4" s="96" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H4" s="96" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I4" s="96" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J4" s="96" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K4" s="96" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L4" s="96" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M4" s="96" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7708,7 +7718,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="97" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B6" s="98" t="n">
         <v>1886</v>
@@ -7766,7 +7776,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="97" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B7" s="98" t="n">
         <v>4000</v>
@@ -7824,7 +7834,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="97" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B8" s="98" t="n">
         <v>3958</v>
@@ -7876,7 +7886,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="97" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B9" s="98" t="n">
         <v>0</v>
@@ -7888,40 +7898,39 @@
         <v>0</v>
       </c>
       <c r="E9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5540/50540</f>
-        <v>5480.8072813613</v>
+        <v>0</v>
       </c>
       <c r="F9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*2000/50540</f>
-        <v>1978.63078749505</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*2000/45000</f>
+        <v>2222.22222222222</v>
       </c>
       <c r="G9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/50540</f>
-        <v>4946.57696873763</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/45000</f>
+        <v>5555.55555555556</v>
       </c>
       <c r="H9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/50540</f>
-        <v>4946.57696873763</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/45000</f>
+        <v>5555.55555555556</v>
       </c>
       <c r="I9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/50540</f>
-        <v>4946.57696873763</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/45000</f>
+        <v>5555.55555555556</v>
       </c>
       <c r="J9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*8000/50540</f>
-        <v>7914.52314998021</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*8000/45000</f>
+        <v>8888.88888888889</v>
       </c>
       <c r="K9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/50540</f>
-        <v>4946.57696873763</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*5000/45000</f>
+        <v>5555.55555555556</v>
       </c>
       <c r="L9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*8000/50540</f>
-        <v>7914.52314998021</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*8000/45000</f>
+        <v>8888.88888888889</v>
       </c>
       <c r="M9" s="99" t="n">
-        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*7000/50540</f>
-        <v>6925.20775623269</v>
+        <f aca="false">(Assumptions!C34-SUM($B9:$D9))*7000/45000</f>
+        <v>7777.77777777778</v>
       </c>
       <c r="N9" s="100" t="n">
         <f aca="false">SUM(B9:D9)</f>
@@ -7934,7 +7943,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="97" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B10" s="98" t="n">
         <v>0</v>
@@ -8001,39 +8010,39 @@
       </c>
       <c r="E11" s="102" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>12548.1907400079</v>
+        <v>7067.38345864662</v>
       </c>
       <c r="F11" s="102" t="n">
         <f aca="false">SUM(F6:F10)</f>
-        <v>19449.683419074</v>
+        <v>19693.2748538012</v>
       </c>
       <c r="G11" s="102" t="n">
         <f aca="false">SUM(G6:G10)</f>
-        <v>56871.2655583435</v>
+        <v>57480.2441451614</v>
       </c>
       <c r="H11" s="102" t="n">
         <f aca="false">SUM(H6:H10)</f>
-        <v>25523.3975917237</v>
+        <v>26132.3761785416</v>
       </c>
       <c r="I11" s="102" t="n">
         <f aca="false">SUM(I6:I10)</f>
-        <v>17052.0270224433</v>
+        <v>17661.0056092613</v>
       </c>
       <c r="J11" s="102" t="n">
         <f aca="false">SUM(J6:J10)</f>
-        <v>52986.8513330753</v>
+        <v>53961.217071984</v>
       </c>
       <c r="K11" s="102" t="n">
         <f aca="false">SUM(K6:K10)</f>
-        <v>20378.3986658375</v>
+        <v>20987.3772526554</v>
       </c>
       <c r="L11" s="102" t="n">
         <f aca="false">SUM(L6:L10)</f>
-        <v>50091.8973547228</v>
+        <v>51066.2630936315</v>
       </c>
       <c r="M11" s="102" t="n">
         <f aca="false">SUM(M6:M10)</f>
-        <v>25414.2883147719</v>
+        <v>26266.858336317</v>
       </c>
       <c r="N11" s="102" t="n">
         <f aca="false">SUM(B11:D11)</f>
@@ -8046,7 +8055,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="97" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B13" s="98" t="n">
         <f aca="false">-ABS(B11*0.1)</f>
@@ -8062,39 +8071,39 @@
       </c>
       <c r="E13" s="99" t="n">
         <f aca="false">-ABS(E11*0.1)</f>
-        <v>-1254.81907400079</v>
+        <v>-706.738345864662</v>
       </c>
       <c r="F13" s="99" t="n">
         <f aca="false">-ABS(F11*0.1)</f>
-        <v>-1944.9683419074</v>
+        <v>-1969.32748538012</v>
       </c>
       <c r="G13" s="99" t="n">
         <f aca="false">-ABS(G11*0.1)</f>
-        <v>-5687.12655583435</v>
+        <v>-5748.02441451615</v>
       </c>
       <c r="H13" s="99" t="n">
         <f aca="false">-ABS(H11*0.1)</f>
-        <v>-2552.33975917237</v>
+        <v>-2613.23761785416</v>
       </c>
       <c r="I13" s="99" t="n">
         <f aca="false">-ABS(I11*0.1)</f>
-        <v>-1705.20270224433</v>
+        <v>-1766.10056092613</v>
       </c>
       <c r="J13" s="99" t="n">
         <f aca="false">-ABS(J11*0.1)</f>
-        <v>-5298.68513330753</v>
+        <v>-5396.1217071984</v>
       </c>
       <c r="K13" s="99" t="n">
         <f aca="false">-ABS(K11*0.1)</f>
-        <v>-2037.83986658375</v>
+        <v>-2098.73772526554</v>
       </c>
       <c r="L13" s="99" t="n">
         <f aca="false">-ABS(L11*0.1)</f>
-        <v>-5009.18973547228</v>
+        <v>-5106.62630936315</v>
       </c>
       <c r="M13" s="99" t="n">
         <f aca="false">-ABS(M11*0.1)</f>
-        <v>-2541.42883147719</v>
+        <v>-2626.6858336317</v>
       </c>
       <c r="N13" s="100" t="n">
         <f aca="false">SUM(B13:D13)</f>
@@ -8123,39 +8132,39 @@
       </c>
       <c r="E14" s="102" t="n">
         <f aca="false">E11+E13</f>
-        <v>11293.3716660071</v>
+        <v>6360.64511278196</v>
       </c>
       <c r="F14" s="102" t="n">
         <f aca="false">F11+F13</f>
-        <v>17504.7150771666</v>
+        <v>17723.9473684211</v>
       </c>
       <c r="G14" s="102" t="n">
         <f aca="false">G11+G13</f>
-        <v>51184.1390025092</v>
+        <v>51732.2197306453</v>
       </c>
       <c r="H14" s="102" t="n">
         <f aca="false">H11+H13</f>
-        <v>22971.0578325513</v>
+        <v>23519.1385606874</v>
       </c>
       <c r="I14" s="102" t="n">
         <f aca="false">I11+I13</f>
-        <v>15346.824320199</v>
+        <v>15894.9050483351</v>
       </c>
       <c r="J14" s="102" t="n">
         <f aca="false">J11+J13</f>
-        <v>47688.1661997678</v>
+        <v>48565.0953647856</v>
       </c>
       <c r="K14" s="102" t="n">
         <f aca="false">K11+K13</f>
-        <v>18340.5587992538</v>
+        <v>18888.6395273899</v>
       </c>
       <c r="L14" s="102" t="n">
         <f aca="false">L11+L13</f>
-        <v>45082.7076192506</v>
+        <v>45959.6367842684</v>
       </c>
       <c r="M14" s="102" t="n">
         <f aca="false">M11+M13</f>
-        <v>22872.8594832947</v>
+        <v>23640.1725026853</v>
       </c>
       <c r="N14" s="102" t="n">
         <f aca="false">N11+N13</f>
@@ -8168,7 +8177,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -8594,7 +8603,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -8613,7 +8622,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="101" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B28" s="102" t="n">
         <f aca="false">B14-B25</f>
@@ -8629,39 +8638,39 @@
       </c>
       <c r="E28" s="102" t="n">
         <f aca="false">E14-E25</f>
-        <v>-3911.65186465622</v>
+        <v>-8844.37841788138</v>
       </c>
       <c r="F28" s="102" t="n">
         <f aca="false">F14-F25</f>
-        <v>-13627.5800517585</v>
+        <v>-13408.3477605041</v>
       </c>
       <c r="G28" s="102" t="n">
         <f aca="false">G14-G25</f>
-        <v>947.680471844898</v>
+        <v>1495.76119998103</v>
       </c>
       <c r="H28" s="102" t="n">
         <f aca="false">H14-H25</f>
-        <v>-36383.0621754437</v>
+        <v>-35834.9814473076</v>
       </c>
       <c r="I28" s="102" t="n">
         <f aca="false">I14-I25</f>
-        <v>-48218.5353705862</v>
+        <v>-47670.4546424501</v>
       </c>
       <c r="J28" s="102" t="n">
         <f aca="false">J14-J25</f>
-        <v>-15877.1934910175</v>
+        <v>-15000.2643259996</v>
       </c>
       <c r="K28" s="102" t="n">
         <f aca="false">K14-K25</f>
-        <v>-47605.2356741401</v>
+        <v>-47057.154946004</v>
       </c>
       <c r="L28" s="102" t="n">
         <f aca="false">L14-L25</f>
-        <v>-20863.0868541434</v>
+        <v>-19986.1576891256</v>
       </c>
       <c r="M28" s="102" t="n">
         <f aca="false">M14-M25</f>
-        <v>-43072.9349900992</v>
+        <v>-42305.6219707086</v>
       </c>
       <c r="N28" s="102" t="n">
         <f aca="false">N14-N25</f>
@@ -8690,39 +8699,39 @@
       </c>
       <c r="E29" s="105" t="n">
         <f aca="false">IF(E11&gt;0,E28/E11,0)</f>
-        <v>-0.311730347880714</v>
+        <v>-1.25143604696597</v>
       </c>
       <c r="F29" s="105" t="n">
         <f aca="false">IF(F11&gt;0,F28/F11,0)</f>
-        <v>-0.700658193664692</v>
+        <v>-0.680859220218317</v>
       </c>
       <c r="G29" s="105" t="n">
         <f aca="false">IF(G11&gt;0,G28/G11,0)</f>
-        <v>0.0166636079317188</v>
+        <v>0.0260221789629775</v>
       </c>
       <c r="H29" s="105" t="n">
         <f aca="false">IF(H11&gt;0,H28/H11,0)</f>
-        <v>-1.42547880017516</v>
+        <v>-1.37128675947705</v>
       </c>
       <c r="I29" s="105" t="n">
         <f aca="false">IF(I11&gt;0,I28/I11,0)</f>
-        <v>-2.82773041041529</v>
+        <v>-2.69919254300289</v>
       </c>
       <c r="J29" s="105" t="n">
         <f aca="false">IF(J11&gt;0,J28/J11,0)</f>
-        <v>-0.299644026613573</v>
+        <v>-0.277982320265115</v>
       </c>
       <c r="K29" s="105" t="n">
         <f aca="false">IF(K11&gt;0,K28/K11,0)</f>
-        <v>-2.33606361592807</v>
+        <v>-2.24216462969665</v>
       </c>
       <c r="L29" s="105" t="n">
         <f aca="false">IF(L11&gt;0,L28/L11,0)</f>
-        <v>-0.416496239030489</v>
+        <v>-0.3913769380869</v>
       </c>
       <c r="M29" s="105" t="n">
         <f aca="false">IF(M11&gt;0,M28/M11,0)</f>
-        <v>-1.69483144507585</v>
+        <v>-1.61060837306973</v>
       </c>
       <c r="N29" s="106" t="n">
         <f aca="false">IF(N11&gt;0,N28/N11,0)</f>
@@ -8735,7 +8744,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -8803,7 +8812,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="101" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B33" s="102" t="n">
         <f aca="false">B28+B32</f>
@@ -8819,39 +8828,39 @@
       </c>
       <c r="E33" s="102" t="n">
         <f aca="false">E28+E32</f>
-        <v>-3911.65186465622</v>
+        <v>-8844.37841788138</v>
       </c>
       <c r="F33" s="102" t="n">
         <f aca="false">F28+F32</f>
-        <v>236372.419948242</v>
+        <v>236591.652239496</v>
       </c>
       <c r="G33" s="102" t="n">
         <f aca="false">G28+G32</f>
-        <v>250947.680471845</v>
+        <v>251495.761199981</v>
       </c>
       <c r="H33" s="102" t="n">
         <f aca="false">H28+H32</f>
-        <v>-36383.0621754437</v>
+        <v>-35834.9814473076</v>
       </c>
       <c r="I33" s="102" t="n">
         <f aca="false">I28+I32</f>
-        <v>-48218.5353705862</v>
+        <v>-47670.4546424501</v>
       </c>
       <c r="J33" s="102" t="n">
         <f aca="false">J28+J32</f>
-        <v>-15877.1934910175</v>
+        <v>-15000.2643259996</v>
       </c>
       <c r="K33" s="102" t="n">
         <f aca="false">K28+K32</f>
-        <v>-47605.2356741401</v>
+        <v>-47057.154946004</v>
       </c>
       <c r="L33" s="102" t="n">
         <f aca="false">L28+L32</f>
-        <v>-20863.0868541434</v>
+        <v>-19986.1576891256</v>
       </c>
       <c r="M33" s="102" t="n">
         <f aca="false">M28+M32</f>
-        <v>-43072.9349900992</v>
+        <v>-42305.6219707086</v>
       </c>
       <c r="N33" s="102" t="n">
         <f aca="false">N28+N32</f>
@@ -8864,7 +8873,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="101" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B34" s="102" t="n">
         <f aca="false">5000+B33</f>
@@ -8880,35 +8889,35 @@
       </c>
       <c r="E34" s="102" t="n">
         <f aca="false">D34+E33</f>
-        <v>15511.3481353438</v>
+        <v>10578.6215821186</v>
       </c>
       <c r="F34" s="102" t="n">
         <f aca="false">E34+F33</f>
-        <v>251883.768083585</v>
+        <v>247170.273821615</v>
       </c>
       <c r="G34" s="102" t="n">
         <f aca="false">F34+G33</f>
-        <v>502831.44855543</v>
+        <v>498666.035021596</v>
       </c>
       <c r="H34" s="102" t="n">
         <f aca="false">G34+H33</f>
-        <v>466448.386379986</v>
+        <v>462831.053574288</v>
       </c>
       <c r="I34" s="102" t="n">
         <f aca="false">H34+I33</f>
-        <v>418229.8510094</v>
+        <v>415160.598931838</v>
       </c>
       <c r="J34" s="102" t="n">
         <f aca="false">I34+J33</f>
-        <v>402352.657518383</v>
+        <v>400160.334605838</v>
       </c>
       <c r="K34" s="102" t="n">
         <f aca="false">J34+K33</f>
-        <v>354747.421844243</v>
+        <v>353103.179659834</v>
       </c>
       <c r="L34" s="102" t="n">
         <f aca="false">K34+L33</f>
-        <v>333884.334990099</v>
+        <v>333117.021970709</v>
       </c>
       <c r="M34" s="102" t="n">
         <f aca="false">L34+M33</f>
@@ -8925,37 +8934,37 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="107" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="40" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="40" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="40" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -8974,7 +8983,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B44" s="23"/>
       <c r="C44" s="23"/>
@@ -8988,7 +8997,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
@@ -9002,7 +9011,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
@@ -9016,7 +9025,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
@@ -9030,7 +9039,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
@@ -9044,7 +9053,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
@@ -9058,7 +9067,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="108" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B50" s="108"/>
       <c r="C50" s="108"/>
@@ -9107,12 +9116,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9141,7 +9150,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B6" s="109" t="n">
         <f aca="false">Assumptions!B7</f>
@@ -9162,7 +9171,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">Assumptions!B9</f>
@@ -9183,7 +9192,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B8" s="109" t="n">
         <f aca="false">Assumptions!B11</f>
@@ -9204,7 +9213,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">Assumptions!B13</f>
@@ -9225,7 +9234,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B10" s="109" t="n">
         <f aca="false">Assumptions!B15</f>
@@ -9246,7 +9255,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B12" s="109" t="n">
         <f aca="false">Assumptions!B17</f>
@@ -9267,7 +9276,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">Assumptions!B19</f>
@@ -9288,7 +9297,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="42" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B14" s="109" t="n">
         <f aca="false">Assumptions!B21</f>
@@ -9309,7 +9318,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">Assumptions!B23</f>
@@ -9330,11 +9339,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">Assumptions!B25</f>
-        <v>70640</v>
+        <v>57382</v>
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">Assumptions!C25</f>
@@ -9498,11 +9507,11 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B26" s="109" t="n">
         <f aca="false">Assumptions!B34</f>
-        <v>18250</v>
+        <v>15000</v>
       </c>
       <c r="C26" s="109" t="n">
         <f aca="false">Assumptions!C34</f>
@@ -9603,7 +9612,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B32" s="109" t="n">
         <f aca="false">Assumptions!B40</f>
@@ -9649,7 +9658,7 @@
       </c>
       <c r="B34" s="48" t="n">
         <f aca="false">B6+B12+B17+B26+B32+B33</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="C34" s="48" t="n">
         <f aca="false">C6+C12+C17+C26+C32+C33</f>
@@ -9666,11 +9675,11 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B35" s="10" t="n">
         <f aca="false">-ABS(B34*Assumptions!B44)</f>
-        <v>-18105.333</v>
+        <v>-16570.089</v>
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">-ABS(C34*Assumptions!C44)</f>
@@ -9691,7 +9700,7 @@
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">B34+B35</f>
-        <v>176575.667</v>
+        <v>161602.911</v>
       </c>
       <c r="C36" s="48" t="n">
         <f aca="false">C34+C35</f>
@@ -9729,7 +9738,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B38" s="109" t="n">
         <f aca="false">-ABS(Assumptions!B68)</f>
@@ -9754,7 +9763,7 @@
       </c>
       <c r="B39" s="41" t="n">
         <f aca="false">B36+B38</f>
-        <v>80575.667</v>
+        <v>65602.911</v>
       </c>
       <c r="C39" s="41" t="n">
         <f aca="false">C36+C38</f>
@@ -9775,7 +9784,7 @@
       </c>
       <c r="B40" s="93" t="n">
         <f aca="false">IF(B34&gt;0,B39/B34,0)</f>
-        <v>0.413885623147611</v>
+        <v>0.368197824586217</v>
       </c>
       <c r="C40" s="93" t="n">
         <f aca="false">IF(C34&gt;0,C39/C34,0)</f>
@@ -9792,7 +9801,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -9801,7 +9810,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B42" s="109" t="n">
         <v>0</v>
@@ -9819,12 +9828,12 @@
         <v>-88475</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>0</v>
@@ -9842,12 +9851,12 @@
         <v>-23739.640043119</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B44" s="48" t="n">
         <f aca="false">B42+B43</f>
@@ -9872,7 +9881,7 @@
       </c>
       <c r="B45" s="41" t="n">
         <f aca="false">B39+B44</f>
-        <v>80575.667</v>
+        <v>65602.911</v>
       </c>
       <c r="C45" s="41" t="n">
         <f aca="false">C39+C44</f>
@@ -9889,11 +9898,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B46" s="93" t="n">
         <f aca="false">IF(B34&gt;0,B45/B34,0)</f>
-        <v>0.413885623147611</v>
+        <v>0.368197824586217</v>
       </c>
       <c r="C46" s="93" t="n">
         <f aca="false">IF(C34&gt;0,C45/C34,0)</f>
@@ -9931,28 +9940,28 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B48" s="48" t="n">
         <f aca="false">Assumptions!B72+B45+B47</f>
-        <v>85575.667</v>
+        <v>70602.911</v>
       </c>
       <c r="C48" s="48" t="n">
         <f aca="false">B48+C45+C47</f>
-        <v>331880.126956881</v>
+        <v>316907.370956881</v>
       </c>
       <c r="D48" s="48" t="n">
         <f aca="false">C48+D45+D47</f>
-        <v>208040.986913762</v>
+        <v>193068.230913762</v>
       </c>
       <c r="E48" s="48" t="n">
         <f aca="false">D48+E45+E47</f>
-        <v>686071.346870643</v>
+        <v>671098.590870643</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -9961,7 +9970,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B51" s="13" t="n">
         <f aca="false">Assumptions!B75</f>
@@ -9982,7 +9991,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B52" s="14" t="n">
         <f aca="false">Assumptions!B76</f>
@@ -10024,11 +10033,11 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B55" s="110" t="n">
         <f aca="false">B34/1</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="C55" s="110" t="n">
         <f aca="false">C34/4</f>
@@ -10091,17 +10100,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10119,12 +10128,12 @@
         <v>5</v>
       </c>
       <c r="F5" s="111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -10134,7 +10143,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B7" s="50" t="n">
         <v>18230</v>
@@ -10149,12 +10158,12 @@
         <v>115000</v>
       </c>
       <c r="F7" s="50" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B8" s="49" t="n">
         <v>2000</v>
@@ -10169,12 +10178,12 @@
         <v>144000</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B9" s="50" t="n">
         <v>73890</v>
@@ -10189,12 +10198,12 @@
         <v>140000</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B10" s="49" t="n">
         <v>0</v>
@@ -10209,12 +10218,12 @@
         <v>100000</v>
       </c>
       <c r="F10" s="49" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B11" s="50" t="n">
         <v>69656</v>
@@ -10229,7 +10238,7 @@
         <v>10000</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10249,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="49" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10276,7 +10285,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -10286,7 +10295,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B16" s="52" t="n">
         <f aca="false">-ABS(B13*0.093)</f>
@@ -10330,7 +10339,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B19" s="50" t="n">
         <v>7911</v>
@@ -10345,12 +10354,12 @@
         <v>72000</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B20" s="49" t="n">
         <v>2469</v>
@@ -10365,12 +10374,12 @@
         <v>36000</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B21" s="50" t="n">
         <v>25000</v>
@@ -10385,12 +10394,12 @@
         <v>80000</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B22" s="49" t="n">
         <v>15994</v>
@@ -10405,12 +10414,12 @@
         <v>25000</v>
       </c>
       <c r="F22" s="49" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B23" s="50" t="n">
         <v>8197</v>
@@ -10425,12 +10434,12 @@
         <v>20000</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B24" s="49" t="n">
         <v>5087</v>
@@ -10445,12 +10454,12 @@
         <v>25000</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B25" s="50" t="n">
         <v>3825</v>
@@ -10465,12 +10474,12 @@
         <v>12000</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B26" s="49" t="n">
         <v>12116</v>
@@ -10485,12 +10494,12 @@
         <v>18000</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B27" s="50" t="n">
         <v>5341</v>
@@ -10505,12 +10514,12 @@
         <v>12000</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B28" s="49" t="n">
         <v>5244</v>
@@ -10525,12 +10534,12 @@
         <v>10000</v>
       </c>
       <c r="F28" s="49" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B29" s="50" t="n">
         <v>9116</v>
@@ -10545,7 +10554,7 @@
         <v>15000</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10572,7 +10581,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -10626,7 +10635,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">5000+B33</f>
@@ -10648,7 +10657,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -10658,11 +10667,11 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B39" s="10" t="n">
         <f aca="false">Projections!B34</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="C39" s="10" t="n">
         <f aca="false">Projections!C34</f>
@@ -10680,7 +10689,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B40" s="52" t="n">
         <f aca="false">B13</f>
@@ -10702,11 +10711,11 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B41" s="110" t="n">
         <f aca="false">B39-B40</f>
-        <v>-17500</v>
+        <v>-34008</v>
       </c>
       <c r="C41" s="110" t="n">
         <f aca="false">C39-C40</f>
@@ -10724,11 +10733,11 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B43" s="10" t="n">
         <f aca="false">Projections!B39</f>
-        <v>80575.667</v>
+        <v>65602.911</v>
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">Projections!C39</f>
@@ -10746,7 +10755,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B44" s="52" t="n">
         <f aca="false">B33</f>
@@ -10768,29 +10777,29 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B46" s="109" t="n">
         <f aca="false">Projections!B48</f>
-        <v>85575.667</v>
+        <v>70602.911</v>
       </c>
       <c r="C46" s="109" t="n">
         <f aca="false">Projections!C48</f>
-        <v>331880.126956881</v>
+        <v>316907.370956881</v>
       </c>
       <c r="D46" s="109" t="n">
         <f aca="false">Projections!D48</f>
-        <v>208040.986913762</v>
+        <v>193068.230913762</v>
       </c>
       <c r="E46" s="109" t="n">
         <f aca="false">Projections!E48</f>
-        <v>686071.346870643</v>
+        <v>671098.590870643</v>
       </c>
       <c r="F46" s="109"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B47" s="110" t="n">
         <f aca="false">B36</f>
@@ -10812,10 +10821,10 @@
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="107" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B49" s="112" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C49" s="112"/>
       <c r="D49" s="112"/>
@@ -10852,17 +10861,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10880,21 +10889,21 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -10911,7 +10920,7 @@
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">Projections!B34</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">Projections!C34</f>
@@ -10938,7 +10947,7 @@
         <v>5972062.5</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10947,7 +10956,7 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">Projections!B45</f>
-        <v>80575.667</v>
+        <v>65602.911</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">Projections!C45</f>
@@ -10974,17 +10983,17 @@
         <v>1613352.46485447</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B8" s="93"/>
       <c r="C8" s="93" t="n">
         <f aca="false">IF(B6&gt;0,(C6-B6)/B6,0)</f>
-        <v>0.619808815446808</v>
+        <v>0.76988657091703</v>
       </c>
       <c r="D8" s="93" t="n">
         <f aca="false">IF(C6&gt;0,(D6-C6)/C6,0)</f>
@@ -11010,7 +11019,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B9" s="113" t="n">
         <v>0.5</v>
@@ -11022,12 +11031,12 @@
       <c r="G9" s="114"/>
       <c r="H9" s="114"/>
       <c r="I9" s="114" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -11040,11 +11049,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B11" s="115" t="n">
         <f aca="false">B6*5</f>
-        <v>973405</v>
+        <v>890865</v>
       </c>
       <c r="C11" s="115" t="n">
         <f aca="false">C6*5</f>
@@ -11071,16 +11080,16 @@
         <v>29860312.5</v>
       </c>
       <c r="I11" s="115" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B12" s="116" t="n">
         <f aca="false">B6*8</f>
-        <v>1557448</v>
+        <v>1425384</v>
       </c>
       <c r="C12" s="116" t="n">
         <f aca="false">C6*8</f>
@@ -11107,16 +11116,16 @@
         <v>47776500</v>
       </c>
       <c r="I12" s="116" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B13" s="115" t="n">
         <f aca="false">B6*12</f>
-        <v>2336172</v>
+        <v>2138076</v>
       </c>
       <c r="C13" s="115" t="n">
         <f aca="false">C6*12</f>
@@ -11143,16 +11152,16 @@
         <v>71664750</v>
       </c>
       <c r="I13" s="115" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B14" s="116" t="n">
         <f aca="false">B6*15</f>
-        <v>2920215</v>
+        <v>2672595</v>
       </c>
       <c r="C14" s="116" t="n">
         <f aca="false">C6*15</f>
@@ -11179,12 +11188,12 @@
         <v>89580937.5</v>
       </c>
       <c r="I14" s="116" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -11197,11 +11206,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B17" s="115" t="n">
         <f aca="false">IF(B7&gt;0,B7*10,0)</f>
-        <v>805756.67</v>
+        <v>656029.11</v>
       </c>
       <c r="C17" s="115" t="n">
         <f aca="false">IF(C7&gt;0,C7*10,0)</f>
@@ -11228,16 +11237,16 @@
         <v>16133524.6485447</v>
       </c>
       <c r="I17" s="115" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B18" s="116" t="n">
         <f aca="false">IF(B7&gt;0,B7*15,0)</f>
-        <v>1208635.005</v>
+        <v>984043.665</v>
       </c>
       <c r="C18" s="116" t="n">
         <f aca="false">IF(C7&gt;0,C7*15,0)</f>
@@ -11264,16 +11273,16 @@
         <v>24200286.9728171</v>
       </c>
       <c r="I18" s="116" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B19" s="115" t="n">
         <f aca="false">IF(B7&gt;0,B7*25,0)</f>
-        <v>2014391.675</v>
+        <v>1640072.775</v>
       </c>
       <c r="C19" s="115" t="n">
         <f aca="false">IF(C7&gt;0,C7*25,0)</f>
@@ -11300,12 +11309,12 @@
         <v>40333811.6213618</v>
       </c>
       <c r="I19" s="115" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -11349,12 +11358,12 @@
         <v>250000</v>
       </c>
       <c r="I22" s="109" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="67" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B24" s="68"/>
       <c r="C24" s="68"/>
@@ -11364,12 +11373,12 @@
       <c r="G24" s="68"/>
       <c r="H24" s="68"/>
       <c r="I24" s="68" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="44" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B25" s="117" t="n">
         <f aca="false">IF(3000000&gt;0,B22/3000000,0)</f>
@@ -11400,16 +11409,16 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="I25" s="117" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="42" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B26" s="118" t="n">
         <f aca="false">B25*B12</f>
-        <v>129787.333333333</v>
+        <v>118782</v>
       </c>
       <c r="C26" s="118" t="n">
         <f aca="false">C25*C12</f>
@@ -11436,16 +11445,16 @@
         <v>3981375</v>
       </c>
       <c r="I26" s="118" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="44" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B27" s="45" t="n">
         <f aca="false">B25*B13</f>
-        <v>194681</v>
+        <v>178173</v>
       </c>
       <c r="C27" s="45" t="n">
         <f aca="false">C25*C13</f>
@@ -11472,16 +11481,16 @@
         <v>5972062.5</v>
       </c>
       <c r="I27" s="45" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="42" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B28" s="119" t="n">
         <f aca="false">IF(B22&gt;0,B26/B22,0)</f>
-        <v>0.519149333333333</v>
+        <v>0.475128</v>
       </c>
       <c r="C28" s="119" t="n">
         <f aca="false">IF(B22&gt;0,C26/B22,0)</f>
@@ -11508,12 +11517,12 @@
         <v>15.9255</v>
       </c>
       <c r="I28" s="119" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="67" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B29" s="68"/>
       <c r="C29" s="68"/>
@@ -11523,12 +11532,12 @@
       <c r="G29" s="68"/>
       <c r="H29" s="68"/>
       <c r="I29" s="68" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="42" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B30" s="120" t="n">
         <f aca="false">IF(Dashboard!B32&gt;0,B22/Dashboard!B32,0)</f>
@@ -11559,16 +11568,16 @@
         <v>0.05</v>
       </c>
       <c r="I30" s="120" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="44" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B31" s="45" t="n">
         <f aca="false">B30*B12</f>
-        <v>77872.4</v>
+        <v>71269.2</v>
       </c>
       <c r="C31" s="45" t="n">
         <f aca="false">C30*C12</f>
@@ -11595,16 +11604,16 @@
         <v>2388825</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="42" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B32" s="118" t="n">
         <f aca="false">B30*B13</f>
-        <v>116808.6</v>
+        <v>106903.8</v>
       </c>
       <c r="C32" s="118" t="n">
         <f aca="false">C30*C13</f>
@@ -11631,16 +11640,16 @@
         <v>3583237.5</v>
       </c>
       <c r="I32" s="118" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B33" s="121" t="n">
         <f aca="false">IF(B22&gt;0,B31/B22,0)</f>
-        <v>0.3114896</v>
+        <v>0.2850768</v>
       </c>
       <c r="C33" s="121" t="n">
         <f aca="false">IF(B22&gt;0,C31/B22,0)</f>
@@ -11667,12 +11676,12 @@
         <v>9.5553</v>
       </c>
       <c r="I33" s="121" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B34" s="68"/>
       <c r="C34" s="68"/>
@@ -11682,12 +11691,12 @@
       <c r="G34" s="68"/>
       <c r="H34" s="68"/>
       <c r="I34" s="68" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B35" s="117" t="n">
         <f aca="false">IF(8000000&gt;0,B22/8000000,0)</f>
@@ -11718,16 +11727,16 @@
         <v>0.03125</v>
       </c>
       <c r="I35" s="117" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="42" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B36" s="118" t="n">
         <f aca="false">B35*B12</f>
-        <v>48670.25</v>
+        <v>44543.25</v>
       </c>
       <c r="C36" s="118" t="n">
         <f aca="false">C35*C12</f>
@@ -11754,16 +11763,16 @@
         <v>1493015.625</v>
       </c>
       <c r="I36" s="118" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B37" s="45" t="n">
         <f aca="false">B35*B13</f>
-        <v>73005.375</v>
+        <v>66814.875</v>
       </c>
       <c r="C37" s="45" t="n">
         <f aca="false">C35*C13</f>
@@ -11790,16 +11799,16 @@
         <v>2239523.4375</v>
       </c>
       <c r="I37" s="45" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="42" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B38" s="119" t="n">
         <f aca="false">IF(B22&gt;0,B36/B22,0)</f>
-        <v>0.194681</v>
+        <v>0.178173</v>
       </c>
       <c r="C38" s="119" t="n">
         <f aca="false">IF(B22&gt;0,C36/B22,0)</f>
@@ -11826,12 +11835,12 @@
         <v>5.9720625</v>
       </c>
       <c r="I38" s="119" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -11857,12 +11866,12 @@
       <c r="G40" s="109"/>
       <c r="H40" s="109"/>
       <c r="I40" s="109" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B41" s="122" t="n">
         <f aca="false">Dashboard!B28</f>
@@ -11875,12 +11884,12 @@
       <c r="G41" s="122"/>
       <c r="H41" s="122"/>
       <c r="I41" s="122" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B42" s="15" t="n">
         <f aca="false">Dashboard!B29</f>
@@ -11893,12 +11902,12 @@
       <c r="G42" s="15"/>
       <c r="H42" s="15"/>
       <c r="I42" s="15" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B43" s="41" t="n">
         <f aca="false">B40*B42</f>
@@ -11911,16 +11920,16 @@
       <c r="G43" s="41"/>
       <c r="H43" s="41"/>
       <c r="I43" s="41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B45" s="10" t="n">
         <f aca="false">B6*B41</f>
-        <v>9734.05</v>
+        <v>8908.65</v>
       </c>
       <c r="C45" s="10" t="n">
         <f aca="false">C6*B41</f>
@@ -11947,28 +11956,28 @@
         <v>298603.125</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B46" s="48" t="n">
         <f aca="false">MIN(B45,B43)</f>
-        <v>9734.05</v>
+        <v>8908.65</v>
       </c>
       <c r="C46" s="48" t="n">
         <f aca="false">MIN(B46+C45,B43)</f>
-        <v>25501.35</v>
+        <v>24675.95</v>
       </c>
       <c r="D46" s="48" t="n">
         <f aca="false">MIN(C46+D45,B43)</f>
-        <v>65377.85</v>
+        <v>64552.45</v>
       </c>
       <c r="E46" s="48" t="n">
         <f aca="false">MIN(D46+E45,B43)</f>
-        <v>153852.85</v>
+        <v>153027.45</v>
       </c>
       <c r="F46" s="48" t="n">
         <f aca="false">MIN(E46+F45,B43)</f>
@@ -11983,28 +11992,28 @@
         <v>225000</v>
       </c>
       <c r="I46" s="48" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B47" s="110" t="n">
         <f aca="false">MAX(0,B43-B46)</f>
-        <v>215265.95</v>
+        <v>216091.35</v>
       </c>
       <c r="C47" s="110" t="n">
         <f aca="false">MAX(0,B43-C46)</f>
-        <v>199498.65</v>
+        <v>200324.05</v>
       </c>
       <c r="D47" s="110" t="n">
         <f aca="false">MAX(0,B43-D46)</f>
-        <v>159622.15</v>
+        <v>160447.55</v>
       </c>
       <c r="E47" s="110" t="n">
         <f aca="false">MAX(0,B43-E46)</f>
-        <v>71147.15</v>
+        <v>71972.55</v>
       </c>
       <c r="F47" s="110" t="n">
         <f aca="false">MAX(0,B43-F46)</f>
@@ -12019,12 +12028,12 @@
         <v>0</v>
       </c>
       <c r="I47" s="110" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B48" s="123" t="str">
         <f aca="false">IF(B47&lt;=0,"YES","NO")</f>
@@ -12058,7 +12067,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -12084,12 +12093,12 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B52" s="8" t="n">
         <f aca="false">Dashboard!B30</f>
@@ -12102,12 +12111,12 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B53" s="13" t="n">
         <f aca="false">Dashboard!B31</f>
@@ -12120,12 +12129,12 @@
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
       <c r="I53" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">PMT(B52,B53,-B51)</f>
@@ -12138,12 +12147,12 @@
       <c r="G54" s="48"/>
       <c r="H54" s="48"/>
       <c r="I54" s="48" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B56" s="52" t="n">
         <v>0</v>
@@ -12172,12 +12181,12 @@
         <v>0</v>
       </c>
       <c r="I56" s="52" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B57" s="110" t="n">
         <f aca="false">B56</f>
@@ -12211,7 +12220,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B58" s="52" t="n">
         <f aca="false">B54*B53-B51</f>
@@ -12224,12 +12233,12 @@
       <c r="G58" s="52"/>
       <c r="H58" s="52"/>
       <c r="I58" s="52" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="17" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -12242,7 +12251,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B61" s="6" t="n">
         <f aca="false">Dashboard!B26</f>
@@ -12255,12 +12264,12 @@
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="42" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B62" s="118" t="n">
         <f aca="false">B22</f>
@@ -12279,7 +12288,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="44" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B63" s="45" t="n">
         <f aca="false">B40</f>
@@ -12298,7 +12307,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B64" s="118" t="n">
         <f aca="false">B51</f>
@@ -12317,11 +12326,11 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B66" s="48" t="n">
         <f aca="false">B45+B56</f>
-        <v>9734.05</v>
+        <v>8908.65</v>
       </c>
       <c r="C66" s="48" t="n">
         <f aca="false">C45+C56</f>
@@ -12348,12 +12357,12 @@
         <v>298603.125</v>
       </c>
       <c r="I66" s="48" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B67" s="94" t="n">
         <f aca="false">IF(B6&gt;0,B66/B6,0)</f>
@@ -12387,7 +12396,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B69" s="122" t="n">
         <f aca="false">Dashboard!B34</f>
@@ -12400,7 +12409,7 @@
       <c r="G69" s="122"/>
       <c r="H69" s="122"/>
       <c r="I69" s="122" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12421,7 +12430,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -12434,7 +12443,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B73" s="23"/>
       <c r="C73" s="23"/>
@@ -12447,7 +12456,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="17" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -12460,182 +12469,182 @@
     </row>
     <row r="76" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>287</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="125" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B77" s="125" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C77" s="125" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D77" s="126" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E77" s="126" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F77" s="125" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="G77" s="125"/>
       <c r="H77" s="125"/>
       <c r="I77" s="126" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="127" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B78" s="127" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C78" s="127" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D78" s="128" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E78" s="128" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F78" s="127" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G78" s="127"/>
       <c r="H78" s="127"/>
       <c r="I78" s="128" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="125" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B79" s="125" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C79" s="125" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D79" s="126" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E79" s="126" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F79" s="125" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G79" s="125"/>
       <c r="H79" s="125"/>
       <c r="I79" s="126" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="127" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B80" s="127" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C80" s="127" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D80" s="128" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E80" s="128" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F80" s="127" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G80" s="127"/>
       <c r="H80" s="127"/>
       <c r="I80" s="128" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="125" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B81" s="125" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C81" s="125" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D81" s="126" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E81" s="126" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F81" s="125" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G81" s="125"/>
       <c r="H81" s="125"/>
       <c r="I81" s="126" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="127" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B82" s="127" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C82" s="127" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D82" s="128" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E82" s="128" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F82" s="127" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G82" s="127"/>
       <c r="H82" s="127"/>
       <c r="I82" s="128" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="17" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -12648,182 +12657,182 @@
     </row>
     <row r="86" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="125" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B87" s="125" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C87" s="125" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D87" s="125" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E87" s="125" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F87" s="125" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="G87" s="125"/>
       <c r="H87" s="125"/>
       <c r="I87" s="126" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="127" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B88" s="127" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C88" s="127" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D88" s="127" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E88" s="127" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F88" s="127" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G88" s="127"/>
       <c r="H88" s="127"/>
       <c r="I88" s="128" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="125" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B89" s="125" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C89" s="125" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D89" s="125" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E89" s="125" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F89" s="125" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G89" s="125"/>
       <c r="H89" s="125"/>
       <c r="I89" s="126" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="127" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B90" s="127" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C90" s="127" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D90" s="127" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E90" s="127" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F90" s="127" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="G90" s="127"/>
       <c r="H90" s="127"/>
       <c r="I90" s="128" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="125" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B91" s="125" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C91" s="125" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D91" s="125" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E91" s="125" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F91" s="125" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="G91" s="125"/>
       <c r="H91" s="125"/>
       <c r="I91" s="126" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="127" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B92" s="127" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C92" s="127" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D92" s="127" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E92" s="127" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F92" s="127" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G92" s="127"/>
       <c r="H92" s="127"/>
       <c r="I92" s="128" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="17" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
@@ -12836,7 +12845,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="23" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B96" s="23"/>
       <c r="C96" s="23"/>
@@ -12849,232 +12858,232 @@
     </row>
     <row r="97" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="125" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B98" s="125" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C98" s="126" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D98" s="126" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E98" s="126" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F98" s="125" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G98" s="125"/>
       <c r="H98" s="125"/>
       <c r="I98" s="126" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="127" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B99" s="127" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C99" s="128" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D99" s="128" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E99" s="128" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F99" s="127" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G99" s="127"/>
       <c r="H99" s="127"/>
       <c r="I99" s="128" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="125" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B100" s="125" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C100" s="126" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D100" s="126" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E100" s="126" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F100" s="125" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="G100" s="125"/>
       <c r="H100" s="125"/>
       <c r="I100" s="126" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="127" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B101" s="127" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C101" s="128" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D101" s="128" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E101" s="128" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F101" s="127" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G101" s="127"/>
       <c r="H101" s="127"/>
       <c r="I101" s="128" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="125" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B102" s="125" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C102" s="126" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D102" s="126" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E102" s="126" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F102" s="125" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G102" s="125"/>
       <c r="H102" s="125"/>
       <c r="I102" s="126" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="127" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B103" s="127" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C103" s="128" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D103" s="128" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E103" s="128" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="F103" s="127" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="G103" s="127"/>
       <c r="H103" s="127"/>
       <c r="I103" s="128" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="125" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B104" s="125" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C104" s="126" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D104" s="126" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E104" s="126" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F104" s="125" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G104" s="125"/>
       <c r="H104" s="125"/>
       <c r="I104" s="126" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="127" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B105" s="127" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C105" s="128" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D105" s="128" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E105" s="128" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F105" s="127" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G105" s="127"/>
       <c r="H105" s="127"/>
       <c r="I105" s="128" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="17" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13087,7 +13096,7 @@
     </row>
     <row r="109" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="129" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B109" s="129"/>
       <c r="C109" s="129"/>
@@ -13100,7 +13109,7 @@
     </row>
     <row r="111" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="130" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B111" s="130"/>
       <c r="C111" s="130"/>
